--- a/QCM5_1_MATH.xlsx
+++ b/QCM5_1_MATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C81D0C5-D22E-4E10-ABB8-2F7BC1C74B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F97084-DD92-4EDA-B695-1656676AEBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,9 +177,6 @@
     <t>$e - 1$</t>
   </si>
   <si>
-    <t>Calculer :$ \left( \int_{1}^{e} t\ln(t)dt$ ;$ \int_{1}^{e} \frac{\ln(t)}{t^2}dt$ ; $\int_{1}^{e^2} \sqrt{t}\ln(t)dt \right)$</t>
-  </si>
-  <si>
     <t>$\int_{-\frac{\pi}{6}}^{\frac{\pi}{6}} \sin^7(t) dt$</t>
   </si>
   <si>
@@ -190,6 +187,9 @@
   </si>
   <si>
     <t>OptionE</t>
+  </si>
+  <si>
+    <t>Calculer :$\left( \int_{1}^{e} t\ln(t)\,dt \ ; \ \int_{1}^{e} \frac{\ln(t)}{t^2}\,dt \ ; \ \int_{1}^{e^2} \sqrt{t}\ln(t)\,dt \right)$</t>
   </si>
 </sst>
 </file>
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>8</v>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -714,7 +714,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -742,7 +742,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -770,7 +770,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
